--- a/Dynamic_model/zenteno_parameters.xlsx
+++ b/Dynamic_model/zenteno_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/cristobal_torrealba_conchaytoro_cl/Documents/Documentos/Proyectos I+D/PI-4497/Resultados/2025/SB_Calibration_2025/Dynamic_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B175C98-77CA-4BD1-A3A0-86EA0CCEB32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{708A1B0C-CE8A-4E9F-84D7-5F51B80A027D}"/>
+    <workbookView xWindow="22944" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{708A1B0C-CE8A-4E9F-84D7-5F51B80A027D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Cristobal Torrealba:</t>
         </r>
@@ -56,7 +56,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 2025</t>
@@ -71,7 +71,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Cristobal Torrealba:</t>
         </r>
@@ -80,7 +80,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 2025+2024</t>
@@ -158,14 +158,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -824,6 +824,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Dynamic_model/zenteno_parameters.xlsx
+++ b/Dynamic_model/zenteno_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/cristobal_torrealba_conchaytoro_cl/Documents/Documentos/Proyectos I+D/PI-4497/Resultados/2025/SB_Calibration_2025/Dynamic_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B175C98-77CA-4BD1-A3A0-86EA0CCEB32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{7B175C98-77CA-4BD1-A3A0-86EA0CCEB32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C58D309D-6C84-4195-8FB0-1F6192972877}"/>
   <bookViews>
-    <workbookView xWindow="22944" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{708A1B0C-CE8A-4E9F-84D7-5F51B80A027D}"/>
+    <workbookView xWindow="1185" yWindow="2175" windowWidth="21690" windowHeight="11145" xr2:uid="{708A1B0C-CE8A-4E9F-84D7-5F51B80A027D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Cristobal Torrealba</author>
+    <author>Cristobal Luis Torrealba Vasquez</author>
   </authors>
   <commentList>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{8E5FD2E3-F0DB-440F-A779-B13AA35D47A0}">
+    <comment ref="P5" authorId="0" shapeId="0" xr:uid="{5A4E6FDE-E7F7-4342-A55B-3838168ED9A5}">
       <text>
         <r>
           <rPr>
@@ -49,7 +49,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Cristobal Torrealba:</t>
+          <t>Cristobal Luis Torrealba Vasquez:</t>
         </r>
         <r>
           <rPr>
@@ -59,11 +59,12 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-2025</t>
+2025
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{3EB21962-1FF1-4D99-855F-32BCFA630B5B}">
+    <comment ref="P6" authorId="0" shapeId="0" xr:uid="{902EE752-FEC4-4A9A-8C7B-2CACEA180B1C}">
       <text>
         <r>
           <rPr>
@@ -73,7 +74,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Cristobal Torrealba:</t>
+          <t>Cristobal Luis Torrealba Vasquez:</t>
         </r>
         <r>
           <rPr>
@@ -83,7 +84,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-2025+2024</t>
+2024 + 2025</t>
         </r>
       </text>
     </comment>
@@ -507,10 +508,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DDF53A-1D96-4DCA-89AC-6729FF7FF5EF}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,7 +558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -604,7 +605,7 @@
         <v>0.62651656888274598</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -651,7 +652,7 @@
         <v>0.62651659999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -698,7 +699,7 @@
         <v>1.1353544376279339</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -745,7 +746,7 @@
         <v>0.57803400000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -792,31 +793,31 @@
         <v>0.96931999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
